--- a/data/trans_orig/Q5412-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Clase-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2007</t>
+          <t>Población según si es capaz de arreglarse en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4746</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,62 +768,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5422</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>950</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4650</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>6,06%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55038</t>
+          <t>55061</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27881</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>29709</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84843</t>
+          <t>84071</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>93,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,97 +1076,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1870</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,68%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1868</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>48960</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>50830</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13918</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>64712</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>66616</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>889</t>
+          <t>932</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>8539</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12472</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>63215</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70865</t>
+          <t>70822</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17599</t>
+          <t>17721</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83681</t>
+          <t>83558</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>93351</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>2698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13462</t>
+          <t>12702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7570</t>
+          <t>6698</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>4764</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16961</t>
+          <t>16596</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,8%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>246610</t>
+          <t>247370</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>256598</t>
+          <t>257374</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,82%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78182</t>
+          <t>79054</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>328863</t>
+          <t>329228</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341170</t>
+          <t>341060</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8994</t>
+          <t>8939</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>944</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9641</t>
+          <t>10053</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3531</t>
+          <t>3647</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14311</t>
+          <t>15538</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>10,24%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>46526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54419</t>
+          <t>54446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86609</t>
+          <t>86197</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95048</t>
+          <t>95306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137404</t>
+          <t>136177</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148184</t>
+          <t>148068</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>89,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1321</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>10737</t>
+          <t>11577</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28886</t>
+          <t>29157</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>11851</t>
+          <t>10520</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>30048</t>
+          <t>28289</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3645</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>396184</t>
+          <t>395913</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>414333</t>
+          <t>413493</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>398667</t>
+          <t>400426</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416864</t>
+          <t>418195</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9752</t>
+          <t>9076</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24096</t>
+          <t>24454</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18436</t>
+          <t>18336</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40086</t>
+          <t>39283</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>30474</t>
+          <t>31414</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>56312</t>
+          <t>57131</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>477455</t>
+          <t>477097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>491799</t>
+          <t>492475</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>636756</t>
+          <t>637559</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>658406</t>
+          <t>658506</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1122081</t>
+          <t>1121262</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1147919</t>
+          <t>1146979</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,41%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2012</t>
+          <t>Población según si es capaz de arreglarse en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4565</t>
+          <t>6343</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5978</t>
+          <t>4801</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7064</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,21%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39353</t>
+          <t>37575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19311</t>
+          <t>20488</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>81,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61891</t>
+          <t>62143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,43%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7194</t>
+          <t>7656</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7360</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2198</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11939</t>
+          <t>12087</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,2%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>53436</t>
+          <t>52974</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11281</t>
+          <t>11542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>17873</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67592</t>
+          <t>67444</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77333</t>
+          <t>77419</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1033</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>9961</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1150</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16519</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108053</t>
+          <t>108692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117541</t>
+          <t>117620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44410</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53465</t>
+          <t>53468</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,31%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>156749</t>
+          <t>157764</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>168993</t>
+          <t>169103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,6%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>14159</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34939</t>
+          <t>34761</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>911</t>
+          <t>766</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7139</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17303</t>
+          <t>17383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38265</t>
+          <t>39216</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196814</t>
+          <t>196992</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217730</t>
+          <t>217594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>51893</t>
+          <t>52956</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59184</t>
+          <t>59329</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>88,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>253583</t>
+          <t>252632</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274545</t>
+          <t>274465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,04%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>11202</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>17508</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>38979</t>
+          <t>36700</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>21384</t>
+          <t>20692</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43869</t>
+          <t>43004</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,77%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92185</t>
+          <t>91494</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101529</t>
+          <t>101598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>149421</t>
+          <t>151700</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>169807</t>
+          <t>170892</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>80,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>247227</t>
+          <t>248092</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>269712</t>
+          <t>270404</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,89%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1132</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>28455</t>
+          <t>27147</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53617</t>
+          <t>52505</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26884</t>
+          <t>27462</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52578</t>
+          <t>51627</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,01%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>856</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1988</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>341087</t>
+          <t>342199</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>366249</t>
+          <t>367557</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,79%</t>
+          <t>93,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>344114</t>
+          <t>345065</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369808</t>
+          <t>369230</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,08%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>25195</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>49738</t>
+          <t>47916</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>61388</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96275</t>
+          <t>96018</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>93958</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>136402</t>
+          <t>134954</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,37%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>509899</t>
+          <t>511721</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>534442</t>
+          <t>535715</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645730</t>
+          <t>645987</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680025</t>
+          <t>680617</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,65%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1165240</t>
+          <t>1166688</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1208321</t>
+          <t>1207684</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2016</t>
+          <t>Población según si es capaz de arreglarse en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6003,97 +6003,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1211</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1933</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5567</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,82%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>15,09%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1211</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5313</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5920</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,15%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,4%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1211</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5544</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68647</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31575</t>
+          <t>31321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99991</t>
+          <t>99615</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>893</t>
+          <t>926</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6568</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>31,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10140</t>
+          <t>10170</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,34%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45837</t>
+          <t>45224</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52451</t>
+          <t>52418</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,93%</t>
+          <t>84,78%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11020</t>
+          <t>11984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,65%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60792</t>
+          <t>60762</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69868</t>
+          <t>69888</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>920</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9944</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7614</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2229</t>
+          <t>2469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110879</t>
+          <t>110317</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119355</t>
+          <t>119341</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38595</t>
+          <t>38494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,52%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153500</t>
+          <t>153336</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164241</t>
+          <t>164001</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,52%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3540</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13839</t>
+          <t>13609</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3543</t>
+          <t>3592</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18329</t>
+          <t>19170</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9728</t>
+          <t>9837</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27406</t>
+          <t>27277</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190017</t>
+          <t>190247</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>199880</t>
+          <t>200316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80717</t>
+          <t>79876</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95503</t>
+          <t>95454</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>80,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275496</t>
+          <t>275625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293174</t>
+          <t>293065</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,75%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14307</t>
+          <t>14178</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2678</t>
+          <t>2702</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15422</t>
+          <t>15841</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>9485</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24741</t>
+          <t>25209</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130914</t>
+          <t>131043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141782</t>
+          <t>141915</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>144128</t>
+          <t>143709</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156872</t>
+          <t>156848</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,33%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>280030</t>
+          <t>279562</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>296576</t>
+          <t>295286</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,89%</t>
         </is>
       </c>
     </row>
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>21312</t>
+          <t>20180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>45394</t>
+          <t>46323</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>367689</t>
+          <t>366760</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>391771</t>
+          <t>392903</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>367689</t>
+          <t>366760</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>391771</t>
+          <t>392903</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,11%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14694</t>
+          <t>14280</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>32597</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,7 +8076,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39717</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71494</t>
+          <t>71327</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>59418</t>
+          <t>58454</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>96603</t>
+          <t>95208</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558757</t>
+          <t>558731</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>576634</t>
+          <t>577048</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8194,7 +8194,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>700870</t>
+          <t>701037</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>732647</t>
+          <t>732248</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,86%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1267089</t>
+          <t>1268484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1304274</t>
+          <t>1305238</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,71%</t>
         </is>
       </c>
     </row>
@@ -8443,7 +8443,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de arreglarse en 2023</t>
+          <t>Población según si es capaz de arreglarse en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8643,7 +8643,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>1706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2055</t>
+          <t>2471</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2927</t>
+          <t>2413</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,4%</t>
         </is>
       </c>
     </row>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105382</t>
+          <t>105873</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63266</t>
+          <t>62850</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8821,7 +8821,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>169973</t>
+          <t>170487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>464</t>
+          <t>457</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>4693</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4750</t>
+          <t>4747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1540</t>
+          <t>1518</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7143</t>
+          <t>7272</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90686</t>
+          <t>90305</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94534</t>
+          <t>94541</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42181</t>
+          <t>42184</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46383</t>
+          <t>46346</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134786</t>
+          <t>134657</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140389</t>
+          <t>140411</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,93%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3318</t>
+          <t>3548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11109</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1533</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6759</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6542</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16325</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98751</t>
+          <t>98521</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>88,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46030</t>
+          <t>45683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51256</t>
+          <t>51105</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>138533</t>
+          <t>139402</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148316</t>
+          <t>148388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,82%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11935</t>
+          <t>11557</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>25418</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24809</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>8862</t>
+          <t>9085</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43576</t>
+          <t>43462</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>212779</t>
+          <t>214222</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226262</t>
+          <t>226640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301884</t>
+          <t>302422</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325313</t>
+          <t>325098</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521314</t>
+          <t>521428</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>556028</t>
+          <t>555805</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,29%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,39%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2013</t>
+          <t>1912</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19597</t>
+          <t>19372</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32835</t>
+          <t>33213</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23269</t>
+          <t>23728</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38172</t>
+          <t>37777</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,73%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83708</t>
+          <t>83963</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>89993</t>
+          <t>90094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,98%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171947</t>
+          <t>171569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185185</t>
+          <t>185410</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>90,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>258616</t>
+          <t>259011</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273519</t>
+          <t>273060</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,14%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,01%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33021</t>
+          <t>32712</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50470</t>
+          <t>50851</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32793</t>
+          <t>32765</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>50896</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>271202</t>
+          <t>270821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288651</t>
+          <t>288960</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274304</t>
+          <t>273980</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292083</t>
+          <t>292111</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39522</t>
+          <t>39741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40909</t>
+          <t>44623</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107043</t>
+          <t>106249</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,51%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70986</t>
+          <t>71470</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134131</t>
+          <t>132757</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598531</t>
+          <t>598312</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>616217</t>
+          <t>615509</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>911145</t>
+          <t>911939</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977279</t>
+          <t>973565</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1522110</t>
+          <t>1523484</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1585255</t>
+          <t>1584771</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5412-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q5412-Clase-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5422</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,05%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>55061</t>
+          <t>55019</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>84071</t>
+          <t>84079</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>886</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8539</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6554</t>
+          <t>7451</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>2534</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12472</t>
+          <t>11913</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63215</t>
+          <t>63474</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70822</t>
+          <t>70868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17721</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>83558</t>
+          <t>84117</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93351</t>
+          <t>93496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,36%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>3476</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12702</t>
+          <t>13322</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>7816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4764</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16596</t>
+          <t>16566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,79%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>247370</t>
+          <t>246750</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>257374</t>
+          <t>256596</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79054</t>
+          <t>77936</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>90,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>329228</t>
+          <t>329258</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341060</t>
+          <t>341063</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1031</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8412</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10053</t>
+          <t>10460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3647</t>
+          <t>3120</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15538</t>
+          <t>14596</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46526</t>
+          <t>47053</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>54446</t>
+          <t>54434</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>86197</t>
+          <t>85790</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>95306</t>
+          <t>95097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>136177</t>
+          <t>137119</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148068</t>
+          <t>148595</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,76%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,94%</t>
         </is>
       </c>
     </row>
@@ -2428,7 +2428,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11577</t>
+          <t>11547</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>29157</t>
+          <t>30028</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10520</t>
+          <t>10999</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28289</t>
+          <t>29220</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>395913</t>
+          <t>395042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>413493</t>
+          <t>413523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>400426</t>
+          <t>399495</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>418195</t>
+          <t>417716</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9076</t>
+          <t>9860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>24454</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>18336</t>
+          <t>18554</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>39283</t>
+          <t>40174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>31414</t>
+          <t>31403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>57131</t>
+          <t>57232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,86%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>477097</t>
+          <t>476774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>492475</t>
+          <t>491691</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>637559</t>
+          <t>636668</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>658506</t>
+          <t>658288</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,2%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1121262</t>
+          <t>1121161</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1146979</t>
+          <t>1146990</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -3373,7 +3373,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4801</t>
+          <t>5530</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3423,7 +3423,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7064</t>
+          <t>7494</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3458,7 +3458,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,83%</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3481,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>37575</t>
+          <t>38563</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -3516,7 +3516,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20488</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62143</t>
+          <t>61713</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7656</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3731,7 +3731,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7360</t>
+          <t>8018</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12087</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>14,41%</t>
         </is>
       </c>
     </row>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>52974</t>
+          <t>53410</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,37%</t>
+          <t>88,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11542</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17873</t>
+          <t>17896</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>57,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>67444</t>
+          <t>68068</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>77419</t>
+          <t>77450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>85,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,38%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1030</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9961</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1147</t>
+          <t>1160</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>3178</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15772</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>108692</t>
+          <t>108350</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>117620</t>
+          <t>117623</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>44199</t>
+          <t>44626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53468</t>
+          <t>53455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>81,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157764</t>
+          <t>157496</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>169103</t>
+          <t>170090</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>15005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34761</t>
+          <t>34687</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>950</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7139</t>
+          <t>7406</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>17383</t>
+          <t>16456</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>39216</t>
+          <t>38164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,08%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196992</t>
+          <t>197066</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>217594</t>
+          <t>216748</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>52956</t>
+          <t>52689</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59329</t>
+          <t>59145</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,12%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>252632</t>
+          <t>253684</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>274465</t>
+          <t>275392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,04%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1098</t>
+          <t>1040</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11202</t>
+          <t>10431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17508</t>
+          <t>18157</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>36700</t>
+          <t>38312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>43004</t>
+          <t>43640</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,99%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>91494</t>
+          <t>92265</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>101598</t>
+          <t>101656</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>151700</t>
+          <t>150088</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>170892</t>
+          <t>170243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>80,52%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>248092</t>
+          <t>247456</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>270404</t>
+          <t>270199</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,82%</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>27147</t>
+          <t>27034</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52505</t>
+          <t>51925</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>27462</t>
+          <t>27747</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51627</t>
+          <t>52506</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>342199</t>
+          <t>342779</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>367557</t>
+          <t>367670</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,7%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,12%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345065</t>
+          <t>344186</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>369230</t>
+          <t>368945</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,01%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>47916</t>
+          <t>47952</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>61388</t>
+          <t>60339</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>96018</t>
+          <t>97532</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>93958</t>
+          <t>93563</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134954</t>
+          <t>134971</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>511721</t>
+          <t>511685</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>535715</t>
+          <t>535644</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>645987</t>
+          <t>644473</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>680617</t>
+          <t>681666</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1166688</t>
+          <t>1166671</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1207684</t>
+          <t>1208079</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5629,7 +5629,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,81%</t>
         </is>
       </c>
     </row>
@@ -6043,7 +6043,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5567</t>
+          <t>6638</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>5219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -6151,7 +6151,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31321</t>
+          <t>30250</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99615</t>
+          <t>100316</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6201,7 +6201,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>907</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8120</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5618</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,86%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>9500</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>45679</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>52418</t>
+          <t>52437</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>11970</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60762</t>
+          <t>61432</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69888</t>
+          <t>69903</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>1220</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9944</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6729,7 +6729,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7715</t>
+          <t>8089</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6744,7 +6744,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2469</t>
+          <t>2378</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,93%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110317</t>
+          <t>111572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>119341</t>
+          <t>119041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38494</t>
+          <t>38120</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -6852,7 +6852,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153336</t>
+          <t>153270</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>164001</t>
+          <t>164092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,11%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13609</t>
+          <t>13855</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19170</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>9520</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27277</t>
+          <t>27991</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190247</t>
+          <t>190001</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>200316</t>
+          <t>200345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79876</t>
+          <t>80027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>95454</t>
+          <t>95442</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,65%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>275625</t>
+          <t>274911</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293065</t>
+          <t>293382</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,75%</t>
+          <t>96,86%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3421</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14178</t>
+          <t>14415</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15841</t>
+          <t>15703</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9485</t>
+          <t>8101</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25209</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,7 +7460,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131043</t>
+          <t>130806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>141915</t>
+          <t>141800</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>143709</t>
+          <t>143847</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>156848</t>
+          <t>156894</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,16%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>279562</t>
+          <t>279554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>295286</t>
+          <t>296670</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>97,34%</t>
         </is>
       </c>
     </row>
@@ -7698,7 +7698,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>45253</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7768,12 +7768,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>20180</t>
+          <t>19933</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46323</t>
+          <t>45253</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,95%</t>
         </is>
       </c>
     </row>
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>366760</t>
+          <t>367830</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>392903</t>
+          <t>393150</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,12 +7881,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>366760</t>
+          <t>367830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>392903</t>
+          <t>393150</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14012</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32597</t>
+          <t>30937</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>38602</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>71327</t>
+          <t>73250</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>58454</t>
+          <t>59432</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95208</t>
+          <t>94639</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8146,12 +8146,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>558731</t>
+          <t>560391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>577048</t>
+          <t>577316</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>701037</t>
+          <t>699114</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>732248</t>
+          <t>733762</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1268484</t>
+          <t>1269053</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1305238</t>
+          <t>1304260</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,12 +8259,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>336</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -8658,7 +8658,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>392</t>
+          <t>408</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2425</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8703,7 +8703,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>723</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>2413</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,25%</t>
         </is>
       </c>
     </row>
@@ -8746,27 +8746,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>107243</t>
+          <t>120086</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105873</t>
+          <t>118775</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -8781,27 +8781,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>64929</t>
+          <t>74151</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62850</t>
+          <t>72134</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,22%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -8816,27 +8816,27 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>172173</t>
+          <t>194237</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170487</t>
+          <t>192520</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -8859,17 +8859,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107579</t>
+          <t>120401</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8894,17 +8894,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>65321</t>
+          <t>74559</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8929,17 +8929,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>172900</t>
+          <t>194960</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8976,32 +8976,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1629</t>
+          <t>1632</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>457</t>
+          <t>484</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4693</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9011,32 +9011,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1944</t>
+          <t>2068</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4747</t>
+          <t>4827</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9046,32 +9046,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>3573</t>
+          <t>3699</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1518</t>
+          <t>1535</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7272</t>
+          <t>7389</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -9089,32 +9089,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>93369</t>
+          <t>103083</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>90305</t>
+          <t>100018</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94541</t>
+          <t>104231</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9124,32 +9124,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44987</t>
+          <t>53317</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42184</t>
+          <t>50558</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46346</t>
+          <t>54941</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>91,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9159,32 +9159,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>138356</t>
+          <t>156401</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>134657</t>
+          <t>152711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>140411</t>
+          <t>158565</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -9202,17 +9202,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>94998</t>
+          <t>104715</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9237,17 +9237,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>46931</t>
+          <t>55385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9272,17 +9272,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>141929</t>
+          <t>160100</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9319,32 +9319,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>6579</t>
+          <t>6775</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3548</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11822</t>
+          <t>11806</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9354,32 +9354,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>4244</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7823</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9389,32 +9389,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>10347</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6470</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15456</t>
+          <t>16741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,82%</t>
         </is>
       </c>
     </row>
@@ -9432,32 +9432,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>95490</t>
+          <t>105696</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>90247</t>
+          <t>100665</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98521</t>
+          <t>108997</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,98%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9467,32 +9467,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49021</t>
+          <t>53726</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>45683</t>
+          <t>50147</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51105</t>
+          <t>56079</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9502,32 +9502,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>144511</t>
+          <t>159422</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>139402</t>
+          <t>153700</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>148388</t>
+          <t>163986</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,82%</t>
+          <t>96,21%</t>
         </is>
       </c>
     </row>
@@ -9545,17 +9545,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>102069</t>
+          <t>112471</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9580,17 +9580,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>57970</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9615,17 +9615,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>154858</t>
+          <t>170441</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9662,32 +9662,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>17203</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11557</t>
+          <t>12341</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>27622</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9697,32 +9697,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8608</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1595</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24271</t>
+          <t>13162</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9732,32 +9732,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>25390</t>
+          <t>27133</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9085</t>
+          <t>19701</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43462</t>
+          <t>36637</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9775,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>220994</t>
+          <t>241480</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>214222</t>
+          <t>232384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>226640</t>
+          <t>247665</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9810,32 +9810,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>318507</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>302422</t>
+          <t>117718</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>325098</t>
+          <t>125645</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9845,32 +9845,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>539500</t>
+          <t>363753</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>521428</t>
+          <t>354249</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555805</t>
+          <t>371185</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>94,96%</t>
         </is>
       </c>
     </row>
@@ -9888,17 +9888,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>238197</t>
+          <t>260006</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9923,17 +9923,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>326693</t>
+          <t>130880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9958,17 +9958,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>564890</t>
+          <t>390886</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10005,32 +10005,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>4255</t>
+          <t>4322</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1912</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10040,32 +10040,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>25806</t>
+          <t>27299</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>19372</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33213</t>
+          <t>35312</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10075,32 +10075,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>30061</t>
+          <t>31621</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23728</t>
+          <t>24798</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>37777</t>
+          <t>40211</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -10118,32 +10118,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>87751</t>
+          <t>96471</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>83963</t>
+          <t>92538</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90094</t>
+          <t>98855</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10153,32 +10153,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>178976</t>
+          <t>192567</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>171569</t>
+          <t>184554</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185410</t>
+          <t>199033</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>87,4%</t>
+          <t>87,58%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10188,32 +10188,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>266727</t>
+          <t>289039</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>259011</t>
+          <t>280449</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>273060</t>
+          <t>295862</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,87%</t>
+          <t>90,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -10231,17 +10231,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92006</t>
+          <t>100793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10266,17 +10266,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>204782</t>
+          <t>219866</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10301,17 +10301,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>296788</t>
+          <t>320660</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10333,7 +10333,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -10383,32 +10383,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>50851</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10418,32 +10418,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>41088</t>
+          <t>44000</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>32765</t>
+          <t>35291</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50896</t>
+          <t>53257</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,26%</t>
         </is>
       </c>
     </row>
@@ -10461,7 +10461,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -10496,32 +10496,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>280584</t>
+          <t>301783</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>270821</t>
+          <t>291486</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>288960</t>
+          <t>310999</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,3%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10531,32 +10531,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>283788</t>
+          <t>305059</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>273980</t>
+          <t>295802</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>292111</t>
+          <t>313768</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,33%</t>
+          <t>84,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -10574,17 +10574,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10609,17 +10609,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>321672</t>
+          <t>345783</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10644,17 +10644,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>324876</t>
+          <t>349059</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10691,32 +10691,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>30001</t>
+          <t>31569</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22544</t>
+          <t>23230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>39741</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10726,32 +10726,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>81184</t>
+          <t>86627</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44623</t>
+          <t>74210</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>106249</t>
+          <t>99581</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10761,32 +10761,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>111186</t>
+          <t>118196</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>71470</t>
+          <t>101464</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132757</t>
+          <t>135040</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -10804,32 +10804,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>608052</t>
+          <t>670094</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>598312</t>
+          <t>660807</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>615509</t>
+          <t>678433</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10839,32 +10839,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>937004</t>
+          <t>797816</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>911939</t>
+          <t>784862</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>973565</t>
+          <t>810233</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>92,03%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10874,32 +10874,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1545055</t>
+          <t>1467910</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1523484</t>
+          <t>1451066</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1584771</t>
+          <t>1484642</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -10917,17 +10917,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>638053</t>
+          <t>701663</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10952,17 +10952,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1018188</t>
+          <t>884443</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>1018188</t>
+          <t>884443</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1018188</t>
+          <t>884443</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10987,17 +10987,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1656241</t>
+          <t>1586106</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1656241</t>
+          <t>1586106</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1656241</t>
+          <t>1586106</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
